--- a/Prac_Stimulus_Configurations.xlsx
+++ b/Prac_Stimulus_Configurations.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Flanker Compatibility Task\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\研究所\碩二下\The Applications of Computer Hardware and Programming Languages in Behavioral Experiments and Big-Data Analyses\Midtern Report\Flanker Compatibility Task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F132B1A-4217-4B66-AD44-396834E6EC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8B7C57-3A89-45FE-9518-F94272256BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11918" yWindow="0" windowWidth="12165" windowHeight="14362" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -33,9 +33,6 @@
     <t>target_type</t>
   </si>
   <si>
-    <t>compatibility</t>
-  </si>
-  <si>
     <t>dist_pos_x</t>
   </si>
   <si>
@@ -50,19 +47,23 @@
     <t>square</t>
   </si>
   <si>
-    <t>comp</t>
-  </si>
-  <si>
     <t>a</t>
   </si>
   <si>
-    <t>incomp</t>
-  </si>
-  <si>
     <t>diamond</t>
   </si>
   <si>
     <t>l</t>
+  </si>
+  <si>
+    <t>cong</t>
+  </si>
+  <si>
+    <t>incong</t>
+  </si>
+  <si>
+    <t>compatibility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -398,16 +399,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
@@ -415,16 +416,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <v>-10</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -435,16 +436,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
         <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -455,16 +456,16 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>10</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -475,16 +476,16 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>-10</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -495,16 +496,16 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
         <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -515,16 +516,16 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7">
         <v>-10</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7">
         <v>2</v>
@@ -535,16 +536,16 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <v>-10</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -555,16 +556,16 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9">
         <v>10</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -575,16 +576,16 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10">
         <v>-10</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -595,16 +596,16 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11" t="s">
         <v>6</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11">
-        <v>10</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -615,16 +616,16 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D12">
         <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -635,16 +636,16 @@
         <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <v>-10</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F13">
         <v>4</v>
@@ -655,16 +656,16 @@
         <v>4</v>
       </c>
       <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
         <v>6</v>
-      </c>
-      <c r="C14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14">
-        <v>10</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
       </c>
       <c r="F14">
         <v>5</v>
@@ -675,16 +676,16 @@
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15">
         <v>-10</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -695,16 +696,16 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D16">
         <v>-10</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F16">
         <v>4</v>
@@ -715,16 +716,16 @@
         <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17">
         <v>10</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F17">
         <v>2</v>

--- a/Prac_Stimulus_Configurations.xlsx
+++ b/Prac_Stimulus_Configurations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\研究所\碩二下\The Applications of Computer Hardware and Programming Languages in Behavioral Experiments and Big-Data Analyses\Midtern Report\Flanker Compatibility Task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8B7C57-3A89-45FE-9518-F94272256BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B2CCB35-D581-4376-9808-0F0A584C085E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
     <t>incong</t>
   </si>
   <si>
-    <t>compatibility</t>
+    <t>condition</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
